--- a/rules/CORE-001034/positive/02/data/unit-test-coreid-CG0562-positive 2.xlsx
+++ b/rules/CORE-001034/positive/02/data/unit-test-coreid-CG0562-positive 2.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc.sharepoint.com/sites/CORERules/Shared Documents/unitTesting/SDTMIG/CG0562/positive/02/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-001034\positive\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{BAD9DE0C-9CE4-4BDE-8D73-ADCB8E04102D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8D30852-511C-424A-838B-526D0F770F99}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B0FDC4-7A0C-4DAB-9F29-1B25A587B8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21240" windowHeight="15270" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="314" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Datasets" sheetId="2" r:id="rId1"/>
-    <sheet name="Library" sheetId="16" r:id="rId2"/>
+    <sheet name="Library" sheetId="16" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="eg.xpt" sheetId="15" r:id="rId3"/>
     <sheet name="vs.xpt" sheetId="17" r:id="rId4"/>
     <sheet name="sv.xpt" sheetId="18" r:id="rId5"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="190">
   <si>
     <t>Filename</t>
   </si>
@@ -258,9 +258,6 @@
     <t>3-3</t>
   </si>
   <si>
-    <t>2022-01-14</t>
-  </si>
-  <si>
     <t>VSSEQ</t>
   </si>
   <si>
@@ -597,13 +594,22 @@
     <t>2013-01-25</t>
   </si>
   <si>
-    <t>2022-01-14T07:00</t>
-  </si>
-  <si>
-    <t>2022-01-20T13:01</t>
-  </si>
-  <si>
-    <t>2022-01-20T13:02</t>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Repetition Number</t>
+  </si>
+  <si>
+    <t>EGREPNUM</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
 </sst>
 </file>
@@ -710,7 +716,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -725,6 +731,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -732,7 +741,7 @@
     <cellStyle name="Normal 3 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Note" xfId="3" builtinId="10"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="31">
     <dxf>
       <font>
         <i/>
@@ -825,6 +834,16 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -909,36 +928,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:B4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B63">
     <sortCondition ref="A2:A63"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Filename" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Label" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Filename" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Label" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D3AC94FD-64DC-485B-AA79-6BACF9296942}" name="Table3821" displayName="Table3821" ref="A1:V10" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
-  <autoFilter ref="A1:V10" xr:uid="{D3AC94FD-64DC-485B-AA79-6BACF9296942}"/>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{D658CD97-7030-4E76-9717-537135449CCC}" name="STUDYID" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{31C22FC0-91C9-4FFF-9D6D-02F1C8B322E9}" name="DOMAIN" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{64E5EB04-8643-45DA-8695-B766328B022D}" name="USUBJID" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{0883A6B3-B5CE-4D13-87E0-B2DCC27C1CC8}" name="EGSEQ" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{A498528B-3D2E-4A7D-9EB5-C9FA5D3FBFD1}" name="EGTESTCD" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{348F7BA2-8006-463D-92C5-8F82D3643B22}" name="EGTEST" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{4020731C-E1E8-44D9-9F01-A82588FA283F}" name="EGORRES" dataDxfId="17"/>
-    <tableColumn id="16" xr3:uid="{4180ED89-7683-4CC1-B096-C064B6F2CE37}" name="EGORRESU" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{EF2DEA1E-25F0-49FB-A08B-28DCBBFDEC59}" name="EGSTRESC" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{F724C116-6250-4F78-96E8-01FF913C4270}" name="EGSTRESN" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{764ED7B9-7C91-4D93-8F42-96DC8CB87BF9}" name="EGSTRESU" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{682798ED-5414-4A99-916A-27F0C2907761}" name="EGSTAT" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{6E1DDD5B-13E5-4E4E-AC7B-C00C5731DDC5}" name="EGREASND" dataDxfId="11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D3AC94FD-64DC-485B-AA79-6BACF9296942}" name="Table3821" displayName="Table3821" ref="A1:W10" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <tableColumns count="23">
+    <tableColumn id="1" xr3:uid="{D658CD97-7030-4E76-9717-537135449CCC}" name="STUDYID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{31C22FC0-91C9-4FFF-9D6D-02F1C8B322E9}" name="DOMAIN" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{64E5EB04-8643-45DA-8695-B766328B022D}" name="USUBJID" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{0883A6B3-B5CE-4D13-87E0-B2DCC27C1CC8}" name="EGSEQ" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{A498528B-3D2E-4A7D-9EB5-C9FA5D3FBFD1}" name="EGTESTCD" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{348F7BA2-8006-463D-92C5-8F82D3643B22}" name="EGTEST" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{4020731C-E1E8-44D9-9F01-A82588FA283F}" name="EGORRES" dataDxfId="18"/>
+    <tableColumn id="16" xr3:uid="{4180ED89-7683-4CC1-B096-C064B6F2CE37}" name="EGORRESU" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{EF2DEA1E-25F0-49FB-A08B-28DCBBFDEC59}" name="EGSTRESC" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{F724C116-6250-4F78-96E8-01FF913C4270}" name="EGSTRESN" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{764ED7B9-7C91-4D93-8F42-96DC8CB87BF9}" name="EGSTRESU" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{682798ED-5414-4A99-916A-27F0C2907761}" name="EGSTAT" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{6E1DDD5B-13E5-4E4E-AC7B-C00C5731DDC5}" name="EGREASND" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{C8B5097C-6ABA-4BEB-A069-FD623192FAD4}" name="EGREPNUM" dataDxfId="11"/>
     <tableColumn id="33" xr3:uid="{212055C9-2E8D-4048-962B-685C1E80F1D4}" name="VISITNUM" dataDxfId="10"/>
     <tableColumn id="34" xr3:uid="{201A4341-2659-45A0-8730-538F2E02D88E}" name="VISIT" dataDxfId="9"/>
     <tableColumn id="38" xr3:uid="{074F6CE3-9BF8-47BE-9020-4485FDAFF8CA}" name="EGDTC" dataDxfId="8"/>
@@ -1263,6 +1282,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6281BC4-1BAD-4CA8-BFF7-3AF8BD159A81}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1289,18 +1334,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1311,46 +1356,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6281BC4-1BAD-4CA8-BFF7-3AF8BD159A81}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E389E6E-C088-4693-8516-B9074AE92C09}">
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" customWidth="1"/>
-    <col min="17" max="17" width="13.85546875" customWidth="1"/>
-    <col min="20" max="20" width="15" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.28515625" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="1.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -1391,34 +1425,37 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>26</v>
       </c>
@@ -1459,34 +1496,37 @@
         <v>38</v>
       </c>
       <c r="N2" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>48</v>
       </c>
@@ -1530,22 +1570,22 @@
         <v>49</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>48</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>48</v>
@@ -1553,8 +1593,11 @@
       <c r="V3" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W3" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>50</v>
       </c>
@@ -1598,44 +1641,47 @@
         <v>8</v>
       </c>
       <c r="O4" s="3">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="P4" s="3">
         <v>50</v>
       </c>
       <c r="Q4" s="3">
+        <v>50</v>
+      </c>
+      <c r="R4" s="3">
         <v>8</v>
       </c>
-      <c r="R4" s="3">
-        <v>50</v>
-      </c>
       <c r="S4" s="3">
+        <v>50</v>
+      </c>
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="T4" s="3">
-        <v>50</v>
-      </c>
       <c r="U4" s="3">
         <v>50</v>
       </c>
       <c r="V4" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="W4" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1658,42 +1704,43 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="6" t="s">
         <v>53</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="V5" s="2"/>
-    </row>
-    <row r="6" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="U5" s="2"/>
+      <c r="V5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="W5" s="2"/>
+    </row>
+    <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1716,42 +1763,46 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="V6" s="2"/>
-    </row>
-    <row r="7" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="U6" s="2"/>
+      <c r="V6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="Y6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1774,42 +1825,43 @@
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="V7" s="2"/>
-    </row>
-    <row r="8" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="U7" s="2"/>
+      <c r="V7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -1832,42 +1884,43 @@
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="P8" s="2" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="s">
+      <c r="R8" s="2"/>
+      <c r="S8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="U8" s="2"/>
+      <c r="V8" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="V8" s="2"/>
-    </row>
-    <row r="9" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="W8" s="2"/>
+    </row>
+    <row r="9" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -1890,42 +1943,43 @@
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="P9" s="2" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="s">
+      <c r="R9" s="2"/>
+      <c r="S9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="U9" s="2"/>
+      <c r="V9" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="V9" s="2"/>
-    </row>
-    <row r="10" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+      <c r="W9" s="2"/>
+    </row>
+    <row r="10" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -1948,33 +2002,35 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O10" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="P10" s="2" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="s">
+      <c r="R10" s="2"/>
+      <c r="S10" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="U10" s="2"/>
+      <c r="V10" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1998,40 +2054,40 @@
         <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>17</v>
@@ -2040,13 +2096,13 @@
         <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="U1"/>
     </row>
@@ -2064,13 +2120,13 @@
         <v>29</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>32</v>
@@ -2091,10 +2147,10 @@
         <v>37</v>
       </c>
       <c r="N2" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>39</v>
@@ -2103,13 +2159,13 @@
         <v>40</v>
       </c>
       <c r="R2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="U2"/>
     </row>
@@ -2244,49 +2300,49 @@
         <v>50</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="J5" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K5" s="5">
         <v>71</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P5" s="5">
         <v>1</v>
       </c>
       <c r="Q5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="S5" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="T5" s="5">
         <v>-7</v>
@@ -2298,49 +2354,49 @@
         <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D6" s="5">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="J6" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K6" s="5">
         <v>71</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P6" s="5">
         <v>2</v>
       </c>
       <c r="Q6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="S6" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="T6" s="5">
         <v>-2</v>
@@ -2352,52 +2408,52 @@
         <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K7" s="5">
         <v>83</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P7" s="5">
         <v>3</v>
       </c>
       <c r="Q7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="S7" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="T7" s="5">
         <v>1</v>
@@ -2409,49 +2465,49 @@
         <v>50</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D8" s="5">
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K8" s="5">
         <v>79</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P8" s="5">
         <v>4</v>
       </c>
       <c r="Q8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="T8" s="5">
         <v>14</v>
@@ -2463,49 +2519,49 @@
         <v>50</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K9" s="5">
         <v>68</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P9" s="5">
         <v>5</v>
       </c>
       <c r="Q9" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S9" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="T9" s="5">
         <v>27</v>
@@ -2517,49 +2573,49 @@
         <v>50</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D10" s="5">
         <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="G10" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="I10" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K10" s="5">
         <v>77</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P10" s="5">
         <v>7</v>
       </c>
       <c r="Q10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S10" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T10" s="5">
         <v>42</v>
@@ -2571,49 +2627,49 @@
         <v>50</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="J11" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K11" s="5">
         <v>71</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P11" s="5">
         <v>7</v>
       </c>
       <c r="Q11" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S11" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T11" s="5">
         <v>42</v>
@@ -2625,49 +2681,49 @@
         <v>50</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D12" s="5">
         <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H12" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K12" s="5">
         <v>69</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P12" s="5">
         <v>7</v>
       </c>
       <c r="Q12" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S12" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T12" s="5">
         <v>42</v>
@@ -2679,49 +2735,49 @@
         <v>50</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D13" s="5">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="G13" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K13" s="5">
         <v>76</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P13" s="5">
         <v>8</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T13" s="5">
         <v>55</v>
@@ -2733,49 +2789,49 @@
         <v>50</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D14" s="5">
         <v>10</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K14" s="5">
         <v>52</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P14" s="5">
         <v>8</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T14" s="5">
         <v>55</v>
@@ -2787,49 +2843,49 @@
         <v>50</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D15" s="5">
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K15" s="5">
         <v>60</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P15" s="5">
         <v>8</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T15" s="5">
         <v>55</v>
@@ -2841,49 +2897,49 @@
         <v>50</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D16" s="5">
         <v>12</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="G16" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K16" s="5">
         <v>68</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P16" s="5">
         <v>201</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="T16" s="5">
         <v>172</v>
@@ -2895,49 +2951,49 @@
         <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H17" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K17" s="5">
         <v>72</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P17" s="5">
         <v>201</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="T17" s="5">
         <v>172</v>
@@ -2949,49 +3005,49 @@
         <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D18" s="5">
         <v>14</v>
       </c>
       <c r="E18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H18" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K18" s="5">
         <v>68</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P18" s="5">
         <v>201</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="T18" s="5">
         <v>172</v>
@@ -3003,49 +3059,49 @@
         <v>50</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D19" s="5">
         <v>21</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J19" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K19" s="5">
         <v>52</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P19" s="5">
         <v>7</v>
       </c>
       <c r="Q19" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S19" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T19" s="5">
         <v>42</v>
@@ -3057,49 +3113,49 @@
         <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D20" s="5">
         <v>22</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J20" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K20" s="5">
         <v>62</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P20" s="5">
         <v>7</v>
       </c>
       <c r="Q20" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S20" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="R20" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S20" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T20" s="5">
         <v>42</v>
@@ -3111,49 +3167,49 @@
         <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D21" s="5">
         <v>23</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J21" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K21" s="5">
         <v>62</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P21" s="5">
         <v>7</v>
       </c>
       <c r="Q21" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S21" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="R21" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="T21" s="5">
         <v>42</v>
@@ -3165,49 +3221,49 @@
         <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D22" s="5">
         <v>24</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I22" s="5" t="s">
+      <c r="J22" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="J22" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="K22" s="5">
         <v>50</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P22" s="5">
         <v>8</v>
       </c>
       <c r="Q22" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="R22" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S22" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="R22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S22" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="T22" s="5">
         <v>55</v>
@@ -3219,49 +3275,49 @@
         <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D23" s="5">
         <v>25</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J23" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K23" s="5">
         <v>52</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P23" s="5">
         <v>8</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T23" s="5">
         <v>55</v>
@@ -3273,49 +3329,49 @@
         <v>50</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D24" s="5">
         <v>26</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J24" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K24" s="5">
         <v>54</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P24" s="5">
         <v>8</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R24" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="T24" s="5">
         <v>55</v>
@@ -3327,49 +3383,49 @@
         <v>50</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D25" s="5">
         <v>27</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J25" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K25" s="5">
         <v>79</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P25" s="5">
         <v>201</v>
       </c>
       <c r="Q25" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S25" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="R25" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S25" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="T25" s="5">
         <v>172</v>
@@ -3381,49 +3437,49 @@
         <v>50</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D26" s="5">
         <v>28</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I26" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J26" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K26" s="5">
         <v>98</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P26" s="5">
         <v>201</v>
       </c>
       <c r="Q26" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S26" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="R26" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S26" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="T26" s="5">
         <v>172</v>
@@ -3435,49 +3491,49 @@
         <v>50</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D27" s="5">
         <v>29</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J27" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K27" s="5">
         <v>94</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P27" s="5">
         <v>201</v>
       </c>
       <c r="Q27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S27" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="R27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="T27" s="5">
         <v>172</v>
@@ -3489,49 +3545,49 @@
         <v>50</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D28" s="5">
         <v>7</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="G28" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K28" s="5">
         <v>59</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P28" s="5">
         <v>8</v>
       </c>
       <c r="Q28" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S28" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="R28" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="T28" s="5">
         <v>55</v>
@@ -3543,49 +3599,49 @@
         <v>50</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D29" s="5">
         <v>8</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H29" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K29" s="5">
         <v>65</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P29" s="5">
         <v>8</v>
       </c>
       <c r="Q29" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S29" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="R29" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S29" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="T29" s="5">
         <v>55</v>
@@ -3597,49 +3653,49 @@
         <v>50</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D30" s="5">
         <v>9</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H30" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K30" s="5">
         <v>68</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P30" s="5">
         <v>8</v>
       </c>
       <c r="Q30" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="R30" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S30" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="R30" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S30" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="T30" s="5">
         <v>55</v>
@@ -3651,49 +3707,49 @@
         <v>50</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D31" s="5">
         <v>17</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J31" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K31" s="5">
         <v>65</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P31" s="5">
         <v>8</v>
       </c>
       <c r="Q31" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="R31" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S31" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="R31" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S31" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="T31" s="5">
         <v>55</v>
@@ -3705,49 +3761,49 @@
         <v>50</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D32" s="5">
         <v>18</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J32" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K32" s="5">
         <v>75</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P32" s="5">
         <v>8</v>
       </c>
       <c r="Q32" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S32" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="R32" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S32" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="T32" s="5">
         <v>55</v>
@@ -3759,49 +3815,49 @@
         <v>50</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D33" s="5">
         <v>19</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="J33" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K33" s="5">
         <v>74</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P33" s="5">
         <v>8</v>
       </c>
       <c r="Q33" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="R33" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S33" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="R33" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S33" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="T33" s="5">
         <v>55</v>
@@ -3847,19 +3903,19 @@
         <v>18</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -3879,19 +3935,19 @@
         <v>40</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -3963,22 +4019,22 @@
         <v>50</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H5" s="5">
         <v>-7</v>
@@ -3992,22 +4048,22 @@
         <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" s="5">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>107</v>
-      </c>
       <c r="G6" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H6" s="5">
         <v>-2</v>
@@ -4021,22 +4077,22 @@
         <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H7" s="5">
         <v>1</v>
@@ -4050,22 +4106,22 @@
         <v>50</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="5">
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H8" s="5">
         <v>14</v>
@@ -4079,22 +4135,22 @@
         <v>50</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>118</v>
-      </c>
       <c r="G9" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H9" s="5">
         <v>27</v>
@@ -4108,22 +4164,22 @@
         <v>50</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10" s="5">
         <v>5.01</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>165</v>
-      </c>
       <c r="G10" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H10" s="5">
         <v>29</v>
@@ -4132,7 +4188,7 @@
         <v>29</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -4140,22 +4196,22 @@
         <v>50</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H11" s="5">
         <v>42</v>
@@ -4169,22 +4225,22 @@
         <v>50</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" s="5">
         <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>126</v>
-      </c>
       <c r="G12" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H12" s="5">
         <v>55</v>
@@ -4198,22 +4254,22 @@
         <v>50</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" s="5">
         <v>101</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="G13" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" s="5">
         <v>77</v>
@@ -4227,22 +4283,22 @@
         <v>50</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14" s="5">
         <v>201</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>130</v>
-      </c>
       <c r="G14" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H14" s="5">
         <v>172</v>
@@ -4256,22 +4312,22 @@
         <v>50</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H15" s="5">
         <v>-16</v>
@@ -4285,22 +4341,22 @@
         <v>50</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D16" s="5">
         <v>2</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H16" s="5">
         <v>-1</v>
@@ -4314,22 +4370,22 @@
         <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D17" s="5">
         <v>3</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H17" s="5">
         <v>1</v>
@@ -4343,22 +4399,22 @@
         <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D18" s="5">
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H18" s="5">
         <v>14</v>
@@ -4372,22 +4428,22 @@
         <v>50</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D19" s="5">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H19" s="5">
         <v>27</v>
@@ -4401,22 +4457,22 @@
         <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D20" s="5">
         <v>7</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H20" s="5">
         <v>41</v>
@@ -4430,22 +4486,22 @@
         <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D21" s="5">
         <v>8</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H21" s="5">
         <v>55</v>
@@ -4459,22 +4515,22 @@
         <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D22" s="5">
         <v>9</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>176</v>
-      </c>
       <c r="G22" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H22" s="5">
         <v>61</v>
@@ -4497,6 +4553,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d36826f407302d9fd93d8089214679b0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="257daeb82d9c284d9d656fb5e9ad601e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4736,16 +4802,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -4756,15 +4812,32 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35F44B09-D790-4525-9F7C-7BDB394DA665}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C4EDDE-D196-4AC8-AD02-E2439740B508}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35F44B09-D790-4525-9F7C-7BDB394DA665}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="63ea592b-d684-45c7-8cdc-fad8f8e6bb41"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
